--- a/artfynd/A 58499-2024 artfynd.xlsx
+++ b/artfynd/A 58499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126494323</v>
+        <v>126494290</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589110</v>
+        <v>589069</v>
       </c>
       <c r="R2" t="n">
-        <v>7292405</v>
+        <v>7292303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126494299</v>
+        <v>126494408</v>
       </c>
       <c r="B3" t="n">
-        <v>75075</v>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589074</v>
+        <v>589128</v>
       </c>
       <c r="R3" t="n">
-        <v>7292327</v>
+        <v>7292532</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,32 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126494315</v>
+        <v>126494312</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126494410</v>
+        <v>126494299</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589128</v>
+        <v>589074</v>
       </c>
       <c r="R5" t="n">
-        <v>7292532</v>
+        <v>7292327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126494312</v>
+        <v>126494330</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589094</v>
+        <v>589166</v>
       </c>
       <c r="R6" t="n">
-        <v>7292393</v>
+        <v>7292432</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,321 +1197,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>126494408</v>
-      </c>
-      <c r="B7" t="n">
-        <v>91259</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Holmträsket, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>589128</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7292532</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Lövrik, luckig grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>126494330</v>
-      </c>
-      <c r="B8" t="n">
-        <v>79598</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Holmträsket, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>589166</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7292432</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Lövrik, luckig grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>126494290</v>
-      </c>
-      <c r="B9" t="n">
-        <v>91241</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Holmträsket, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>589069</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7292303</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Lövrik, luckig grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58499-2024 artfynd.xlsx
+++ b/artfynd/A 58499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494290</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494408</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494312</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494299</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>